--- a/case/03-proposals/helix/HLX-003.xlsx
+++ b/case/03-proposals/helix/HLX-003.xlsx
@@ -57,7 +57,7 @@
     <t>Case notice</t>
   </si>
   <si>
-    <t>Fictional training case; all people, organisations, products, rules and events are invented. This is not A*STAR policy or Singapore procurement law.</t>
+    <t>Fictional training case; all people, organisations, products, rules and events are invented. This is not organisational policy or Singapore procurement law.</t>
   </si>
   <si>
     <t>Line</t>
